--- a/verification/cases/roundtrip/date_formats/init.xlsx
+++ b/verification/cases/roundtrip/date_formats/init.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10323"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr date1904="1" showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anthonyschott/repos/poi/test-data/spreadsheet/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\frl\AppData\Local\Temp\xlsx-export-inits-3946636136\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8ED41FF-7D7D-0C41-B58A-8FF213C6497B}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AA6D9413-2E8F-4BE1-AA51-888BDFEEEE13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="29980" windowHeight="18440" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Flags" sheetId="2" r:id="rId1"/>
@@ -18,6 +18,17 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="http://schemas.microsoft.com/office/mac/excel/2008/main">
       <mx:ArchID Flags="2"/>
     </ext>
@@ -215,7 +226,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd\-mmm\-yyyy\ hh:mm:ss.000"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Verdana"/>
@@ -264,7 +275,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -294,15 +305,6 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -644,15 +646,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="13"/>
+  <sheetFormatPr defaultColWidth="10.6328125" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.6640625" style="7"/>
+    <col min="1" max="1" width="10.6328125" style="7"/>
     <col min="2" max="2" width="17" style="8" customWidth="1"/>
-    <col min="3" max="3" width="34.83203125" style="8" customWidth="1"/>
-    <col min="4" max="16384" width="10.6640625" style="1"/>
+    <col min="3" max="3" width="34.81640625" style="8" customWidth="1"/>
+    <col min="4" max="16384" width="10.6328125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="4" customFormat="1" ht="14">
+    <row r="1" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>31</v>
       </c>
@@ -663,7 +665,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="14">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="7" t="s">
         <v>30</v>
       </c>
@@ -671,7 +673,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="14">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="7" t="s">
         <v>35</v>
       </c>
@@ -680,7 +682,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="28">
+    <row r="4" spans="1:3" ht="25.2" x14ac:dyDescent="0.2">
       <c r="A4" s="7" t="s">
         <v>37</v>
       </c>
@@ -706,16 +708,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D46"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="13"/>
+  <sheetFormatPr defaultColWidth="10.6328125" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="29.6640625" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.6640625" style="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="49.5" style="13" customWidth="1"/>
+    <col min="1" max="1" width="29.6328125" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.6328125" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="49.453125" style="2" customWidth="1"/>
     <col min="4" max="4" width="13" style="2" customWidth="1"/>
-    <col min="5" max="16384" width="10.6640625" style="2"/>
+    <col min="5" max="16384" width="10.6328125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="3" customFormat="1">
+    <row r="1" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>18</v>
       </c>
@@ -729,7 +731,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="9" t="str">
         <f t="shared" ref="A2:A20" si="0">TEXT(C2, B2)</f>
         <v>11-10-52</v>
@@ -744,7 +746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="9" t="str">
         <f t="shared" ref="A3" si="1">TEXT(C3, B3)</f>
         <v>11-10-52</v>
@@ -759,7 +761,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="9" t="str">
         <f t="shared" ref="A4:A7" si="2">TEXT(C4, B4)</f>
         <v>Sat-Oct-1952</v>
@@ -774,7 +776,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="9" t="str">
         <f t="shared" si="2"/>
         <v>Saturday-October-1952</v>
@@ -789,7 +791,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="9" t="str">
         <f t="shared" si="2"/>
         <v>11-10-52</v>
@@ -804,7 +806,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="9" t="str">
         <f t="shared" si="2"/>
         <v>11-10-52</v>
@@ -819,7 +821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="9" t="str">
         <f t="shared" ref="A8:A14" si="3">TEXT(C8, B8)</f>
         <v>Sat-Oct-1952</v>
@@ -834,7 +836,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="9" t="str">
         <f t="shared" si="3"/>
         <v>Saturday-October-1952</v>
@@ -849,7 +851,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="9" t="str">
         <f t="shared" si="3"/>
         <v>14:35:27</v>
@@ -864,7 +866,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="9" t="str">
         <f t="shared" si="3"/>
         <v>02:35:27 p</v>
@@ -879,7 +881,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="9" t="str">
         <f t="shared" si="3"/>
         <v>2:35:27.000 P</v>
@@ -894,7 +896,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="9" t="str">
         <f t="shared" si="3"/>
         <v>02:35:27.000 PM</v>
@@ -909,7 +911,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="9" t="str">
         <f t="shared" si="3"/>
         <v>11-10-52 14:35:27</v>
@@ -924,7 +926,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="9" t="str">
         <f t="shared" si="0"/>
         <v>14:35:27</v>
@@ -939,7 +941,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="9" t="str">
         <f t="shared" si="0"/>
         <v>02:35:27 P</v>
@@ -954,7 +956,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" s="9" t="str">
         <f t="shared" si="0"/>
         <v>2:35:27.00 p</v>
@@ -969,7 +971,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" s="9" t="str">
         <f t="shared" si="0"/>
         <v>02:35:27.000 PM</v>
@@ -984,7 +986,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" s="9" t="str">
         <f t="shared" si="0"/>
         <v>11-10-52 14:35:27</v>
@@ -999,7 +1001,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" s="9" t="str">
         <f t="shared" si="0"/>
         <v>Saturday-October-1952 2:35:27 PM</v>
@@ -1010,11 +1012,11 @@
       <c r="C20" s="10">
         <v>17816.607951388887</v>
       </c>
-      <c r="D20" s="12" t="s">
+      <c r="D20" s="7" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" s="9" t="str">
         <f t="shared" ref="A21:A39" si="4">TEXT(C21, B21)</f>
         <v>1-2-03</v>
@@ -1029,7 +1031,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" s="9" t="str">
         <f t="shared" si="4"/>
         <v>01-02-03</v>
@@ -1044,7 +1046,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:4">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" s="9" t="str">
         <f t="shared" si="4"/>
         <v>Sat-Feb-2003</v>
@@ -1059,7 +1061,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" s="9" t="str">
         <f t="shared" si="4"/>
         <v>Saturday-February-2003</v>
@@ -1074,7 +1076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:4">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" s="9" t="str">
         <f t="shared" si="4"/>
         <v>1-2-03</v>
@@ -1089,7 +1091,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:4">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" s="9" t="str">
         <f t="shared" si="4"/>
         <v>01-02-03</v>
@@ -1104,7 +1106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:4">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" s="9" t="str">
         <f t="shared" si="4"/>
         <v>Sat-Feb-2003</v>
@@ -1119,7 +1121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:4">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" s="9" t="str">
         <f t="shared" si="4"/>
         <v>Saturday-February-2003</v>
@@ -1134,7 +1136,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:4">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" s="9" t="str">
         <f t="shared" si="4"/>
         <v>4:5:6</v>
@@ -1149,7 +1151,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:4">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" s="9" t="str">
         <f t="shared" si="4"/>
         <v>04:05:06 a</v>
@@ -1164,7 +1166,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:4">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" s="9" t="str">
         <f t="shared" si="4"/>
         <v>4:5:6.01 A</v>
@@ -1179,7 +1181,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:4">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" s="9" t="str">
         <f t="shared" si="4"/>
         <v>04:05:06.009 AM</v>
@@ -1194,7 +1196,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:4">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" s="9" t="str">
         <f t="shared" si="4"/>
         <v>1-2-03 4:5:6</v>
@@ -1209,7 +1211,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:4">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" s="9" t="str">
         <f t="shared" si="4"/>
         <v>4:5:6</v>
@@ -1224,7 +1226,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:4">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" s="9" t="str">
         <f t="shared" si="4"/>
         <v>04:05:06 A</v>
@@ -1239,7 +1241,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:4">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" s="9" t="str">
         <f t="shared" si="4"/>
         <v>4:5:6.01 a</v>
@@ -1254,7 +1256,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:4">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" s="9" t="str">
         <f t="shared" si="4"/>
         <v>04:05:06.009 AM</v>
@@ -1269,7 +1271,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:4">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" s="9" t="str">
         <f t="shared" si="4"/>
         <v>1-2-03 4:5:6</v>
@@ -1284,7 +1286,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="39" spans="1:4">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39" s="9" t="str">
         <f t="shared" si="4"/>
         <v>Saturday-February-2003 4:5:6 AM</v>
@@ -1295,11 +1297,11 @@
       <c r="C39" s="10">
         <v>36191.170208437499</v>
       </c>
-      <c r="D39" s="12" t="s">
+      <c r="D39" s="7" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="40" spans="1:4">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40" s="9" t="str">
         <f t="shared" ref="A40:A46" si="5">TEXT(C40, B40)</f>
         <v>4:5:6.01</v>
@@ -1314,12 +1316,12 @@
         <v>38</v>
       </c>
     </row>
-    <row r="41" spans="1:4">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A41" s="9" t="str">
         <f t="shared" si="5"/>
         <v>01-01-2025</v>
       </c>
-      <c r="B41" s="11" t="s">
+      <c r="B41" s="9" t="s">
         <v>11</v>
       </c>
       <c r="C41" s="10">
@@ -1329,27 +1331,27 @@
         <v>39</v>
       </c>
     </row>
-    <row r="42" spans="1:4">
-      <c r="A42" s="11" t="str">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A42" s="9" t="str">
         <f t="shared" si="5"/>
         <v>14:35</v>
       </c>
-      <c r="B42" s="11" t="s">
+      <c r="B42" s="9" t="s">
         <v>41</v>
       </c>
       <c r="C42" s="10">
         <v>17816.607951388887</v>
       </c>
-      <c r="D42" s="12" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4">
-      <c r="A43" s="11" t="str">
+      <c r="D42" s="7" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A43" s="9" t="str">
         <f t="shared" si="5"/>
         <v>11 days 14</v>
       </c>
-      <c r="B43" s="14" t="s">
+      <c r="B43" s="11" t="s">
         <v>44</v>
       </c>
       <c r="C43" s="10">
@@ -1359,12 +1361,12 @@
         <v>43</v>
       </c>
     </row>
-    <row r="44" spans="1:4">
-      <c r="A44" s="11" t="str">
+    <row r="44" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A44" s="9" t="str">
         <f t="shared" si="5"/>
         <v>11 days 14</v>
       </c>
-      <c r="B44" s="14" t="s">
+      <c r="B44" s="11" t="s">
         <v>45</v>
       </c>
       <c r="C44" s="10">
@@ -1374,12 +1376,12 @@
         <v>43</v>
       </c>
     </row>
-    <row r="45" spans="1:4">
-      <c r="A45" s="11" t="str">
+    <row r="45" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A45" s="9" t="str">
         <f t="shared" si="5"/>
         <v>11 days 2 p</v>
       </c>
-      <c r="B45" s="14" t="s">
+      <c r="B45" s="11" t="s">
         <v>46</v>
       </c>
       <c r="C45" s="10">
@@ -1389,12 +1391,12 @@
         <v>43</v>
       </c>
     </row>
-    <row r="46" spans="1:4">
-      <c r="A46" s="11" t="str">
+    <row r="46" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A46" s="9" t="str">
         <f t="shared" si="5"/>
         <v>11 days 2 PM</v>
       </c>
-      <c r="B46" s="14" t="s">
+      <c r="B46" s="11" t="s">
         <v>47</v>
       </c>
       <c r="C46" s="10">
